--- a/data/solar/reports/Plant_Report_16-10-2026.xlsx
+++ b/data/solar/reports/Plant_Report_16-10-2026.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
   <si>
     <t>${title}</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -672,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:M12"/>
+  <dimension ref="A4:M25"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="13" customWidth="true" style="1" width="23.125"/>
@@ -750,11 +750,11 @@
       <c r="D3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>42</v>
+      <c r="E3" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>0.0</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>0.0</v>
@@ -1309,6 +1309,763 @@
       </c>
       <c r="M12" s="9" t="n">
         <v>32.52</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" ht="24.95">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 10:00:00</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>11.48</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" ht="24.95">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 11:00:00</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>16.48</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>13.96</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" ht="24.95">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:00:00</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>67.6</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" ht="24.95">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:00:00</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L16" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>10.04</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" ht="24.95">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 14:00:00</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>9.78</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>12.36</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" ht="24.95">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:00:00</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" ht="24.95">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 16:00:00</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>8.53</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>8.53</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" ht="24.95">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:00:00</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" ht="24.95">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:00:00</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" ht="24.95">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 19:00:00</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" ht="24.95">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 20:00:00</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M23" s="9" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" ht="24.95">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 21:00:00</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M24" s="9" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" ht="24.95">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:00:00</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
